--- a/uploads_templates/uploads_for_validation/5.line_resource_requirements.xlsx
+++ b/uploads_templates/uploads_for_validation/5.line_resource_requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Moove\RCCP\uploads_templates\uploads_for_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A65FAFA-F1AE-4892-B92F-0525B13C461F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319A4E29-611D-416D-AAB1-61E225F8E698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17580" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
   <si>
     <t>Production line code (e.g. A101). Must exist in the masterdata.</t>
   </si>
@@ -90,6 +90,39 @@
   </si>
   <si>
     <t>A103</t>
+  </si>
+  <si>
+    <t>A201</t>
+  </si>
+  <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>A302</t>
+  </si>
+  <si>
+    <t>A303</t>
+  </si>
+  <si>
+    <t>A304</t>
+  </si>
+  <si>
+    <t>A305</t>
+  </si>
+  <si>
+    <t>A307</t>
+  </si>
+  <si>
+    <t>A308</t>
+  </si>
+  <si>
+    <t>A501</t>
+  </si>
+  <si>
+    <t>A502</t>
+  </si>
+  <si>
+    <t>A401</t>
   </si>
 </sst>
 </file>
@@ -500,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -592,6 +625,248 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3">
         <v>1</v>
       </c>
     </row>
